--- a/مؤشرات_وزارة_التعليم.xlsx
+++ b/مؤشرات_وزارة_التعليم.xlsx
@@ -55,11 +55,6 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00AAAAAA"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00B03A2E"/>
       <sz val="10"/>
@@ -68,6 +63,11 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="008A8A8A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00AAAAAA"/>
       <sz val="10"/>
     </font>
     <font>
@@ -178,10 +178,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -193,7 +193,7 @@
     <xf numFmtId="2" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P31"/>
+  <dimension ref="A1:Q31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -583,12 +583,13 @@
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -644,30 +645,35 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>Q1-2026</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>مستهدف_جدة</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>إنجاز_مستهدف_جدة %</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>الحالة_جدة</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>مستهدف_وطني</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>إنجاز_مستهدف_وطني %</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>الحالة_وطني</t>
         </is>
@@ -712,28 +718,27 @@
       <c r="J2" s="9" t="n">
         <v>0.3261</v>
       </c>
-      <c r="K2" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L2" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M2" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N2" s="8" t="n">
-        <v>0.4</v>
+      <c r="K2" s="8" t="n">
+        <v>0.2523</v>
+      </c>
+      <c r="L2" s="8" t="n">
+        <v>0.4785</v>
+      </c>
+      <c r="M2" s="8" t="n">
+        <v>0.5273</v>
+      </c>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>غير محقق</t>
+        </is>
       </c>
       <c r="O2" s="8" t="n">
-        <v>0.8151999999999999</v>
-      </c>
-      <c r="P2" s="11" t="inlineStr">
+        <v>0.4704</v>
+      </c>
+      <c r="P2" s="8" t="n">
+        <v>0.5364</v>
+      </c>
+      <c r="Q2" s="10" t="inlineStr">
         <is>
           <t>غير محقق</t>
         </is>
@@ -775,27 +780,30 @@
       <c r="I3" s="8" t="n">
         <v>0.0204</v>
       </c>
-      <c r="J3" s="9" t="n">
+      <c r="J3" s="8" t="n">
         <v>0.0227</v>
       </c>
-      <c r="K3" s="8" t="n">
-        <v>0.0233</v>
+      <c r="K3" s="9" t="n">
+        <v>0.0621</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>0.9742000000000001</v>
-      </c>
-      <c r="M3" s="11" t="inlineStr">
-        <is>
-          <t>غير محقق</t>
-        </is>
-      </c>
-      <c r="N3" s="8" t="n">
-        <v>0.0197</v>
+        <v>0.0258</v>
+      </c>
+      <c r="M3" s="8" t="n">
+        <v>2.407</v>
+      </c>
+      <c r="N3" s="11" t="inlineStr">
+        <is>
+          <t>محقق</t>
+        </is>
       </c>
       <c r="O3" s="8" t="n">
-        <v>1.1523</v>
-      </c>
-      <c r="P3" s="12" t="inlineStr">
+        <v>0.0241</v>
+      </c>
+      <c r="P3" s="8" t="n">
+        <v>2.5768</v>
+      </c>
+      <c r="Q3" s="11" t="inlineStr">
         <is>
           <t>محقق</t>
         </is>
@@ -835,27 +843,30 @@
       <c r="I4" s="8" t="n">
         <v>0.3657</v>
       </c>
-      <c r="J4" s="9" t="n">
+      <c r="J4" s="8" t="n">
         <v>0.46</v>
       </c>
-      <c r="K4" s="8" t="n">
-        <v>0.1624</v>
+      <c r="K4" s="9" t="n">
+        <v>0.8482</v>
       </c>
       <c r="L4" s="8" t="n">
-        <v>2.8325</v>
-      </c>
-      <c r="M4" s="12" t="inlineStr">
+        <v>0.46</v>
+      </c>
+      <c r="M4" s="8" t="n">
+        <v>1.8439</v>
+      </c>
+      <c r="N4" s="11" t="inlineStr">
         <is>
           <t>محقق</t>
         </is>
       </c>
-      <c r="N4" s="8" t="n">
-        <v>0.2</v>
-      </c>
       <c r="O4" s="8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P4" s="12" t="inlineStr">
+        <v>0.2169</v>
+      </c>
+      <c r="P4" s="8" t="n">
+        <v>3.9106</v>
+      </c>
+      <c r="Q4" s="11" t="inlineStr">
         <is>
           <t>محقق</t>
         </is>
@@ -899,23 +910,26 @@
         <v>0.897</v>
       </c>
       <c r="K5" s="8" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="L5" s="8" t="n">
         <v>0.8079</v>
       </c>
-      <c r="L5" s="8" t="n">
+      <c r="M5" s="8" t="n">
         <v>1.1103</v>
       </c>
-      <c r="M5" s="12" t="inlineStr">
+      <c r="N5" s="11" t="inlineStr">
         <is>
           <t>محقق</t>
         </is>
       </c>
-      <c r="N5" s="8" t="n">
+      <c r="O5" s="8" t="n">
         <v>0.8686</v>
       </c>
-      <c r="O5" s="8" t="n">
+      <c r="P5" s="8" t="n">
         <v>1.0327</v>
       </c>
-      <c r="P5" s="12" t="inlineStr">
+      <c r="Q5" s="11" t="inlineStr">
         <is>
           <t>محقق</t>
         </is>
@@ -935,9 +949,9 @@
           <t>قسم التوجيه الطلابي</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>مفعل</t>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>غير مفعل</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -960,24 +974,25 @@
       <c r="J6" s="14" t="n">
         <v>76.72</v>
       </c>
-      <c r="K6" s="14" t="n">
+      <c r="K6" s="2" t="n"/>
+      <c r="L6" s="14" t="n">
         <v>80.63</v>
       </c>
-      <c r="L6" s="8" t="n">
+      <c r="M6" s="8" t="n">
         <v>0.9515</v>
       </c>
-      <c r="M6" s="11" t="inlineStr">
+      <c r="N6" s="10" t="inlineStr">
         <is>
           <t>غير محقق</t>
         </is>
       </c>
-      <c r="N6" s="14" t="n">
+      <c r="O6" s="14" t="n">
         <v>77.65000000000001</v>
       </c>
-      <c r="O6" s="8" t="n">
+      <c r="P6" s="8" t="n">
         <v>0.988</v>
       </c>
-      <c r="P6" s="11" t="inlineStr">
+      <c r="Q6" s="10" t="inlineStr">
         <is>
           <t>غير محقق</t>
         </is>
@@ -1021,27 +1036,30 @@
         <v>0.7879</v>
       </c>
       <c r="K7" s="8" t="n">
+        <v>0.7879</v>
+      </c>
+      <c r="L7" s="8" t="n">
         <v>0.9005</v>
       </c>
-      <c r="L7" s="8" t="n">
+      <c r="M7" s="8" t="n">
         <v>0.875</v>
       </c>
-      <c r="M7" s="11" t="inlineStr">
+      <c r="N7" s="10" t="inlineStr">
         <is>
           <t>غير محقق</t>
         </is>
       </c>
-      <c r="N7" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O7" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P7" s="10" t="inlineStr">
+      <c r="O7" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P7" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q7" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1061,9 +1079,9 @@
           <t>قسم التوجيه الطلابي</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>مفعل</t>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>غير مفعل</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -1084,24 +1102,25 @@
       <c r="J8" s="8" t="n">
         <v>0.715</v>
       </c>
-      <c r="K8" s="8" t="n">
+      <c r="K8" s="2" t="n"/>
+      <c r="L8" s="8" t="n">
         <v>0.8120000000000001</v>
       </c>
-      <c r="L8" s="8" t="n">
+      <c r="M8" s="8" t="n">
         <v>0.8804999999999999</v>
       </c>
-      <c r="M8" s="11" t="inlineStr">
+      <c r="N8" s="10" t="inlineStr">
         <is>
           <t>غير محقق</t>
         </is>
       </c>
-      <c r="N8" s="8" t="n">
+      <c r="O8" s="8" t="n">
         <v>0.85</v>
       </c>
-      <c r="O8" s="8" t="n">
+      <c r="P8" s="8" t="n">
         <v>0.8412000000000001</v>
       </c>
-      <c r="P8" s="11" t="inlineStr">
+      <c r="Q8" s="10" t="inlineStr">
         <is>
           <t>غير محقق</t>
         </is>
@@ -1147,23 +1166,26 @@
         <v>0.065</v>
       </c>
       <c r="K9" s="8" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="L9" s="8" t="n">
         <v>0.1524</v>
       </c>
-      <c r="L9" s="8" t="n">
+      <c r="M9" s="8" t="n">
         <v>0.4265</v>
       </c>
-      <c r="M9" s="11" t="inlineStr">
+      <c r="N9" s="10" t="inlineStr">
         <is>
           <t>غير محقق</t>
         </is>
       </c>
-      <c r="N9" s="8" t="n">
+      <c r="O9" s="8" t="n">
         <v>0.1875</v>
       </c>
-      <c r="O9" s="8" t="n">
+      <c r="P9" s="8" t="n">
         <v>0.3467</v>
       </c>
-      <c r="P9" s="11" t="inlineStr">
+      <c r="Q9" s="10" t="inlineStr">
         <is>
           <t>غير محقق</t>
         </is>
@@ -1207,23 +1229,26 @@
         <v>0.7314000000000001</v>
       </c>
       <c r="K10" s="8" t="n">
+        <v>0.7314000000000001</v>
+      </c>
+      <c r="L10" s="8" t="n">
         <v>0.8849000000000001</v>
       </c>
-      <c r="L10" s="8" t="n">
+      <c r="M10" s="8" t="n">
         <v>0.8265</v>
       </c>
-      <c r="M10" s="11" t="inlineStr">
+      <c r="N10" s="10" t="inlineStr">
         <is>
           <t>غير محقق</t>
         </is>
       </c>
-      <c r="N10" s="8" t="n">
+      <c r="O10" s="8" t="n">
         <v>0.6579999999999999</v>
       </c>
-      <c r="O10" s="8" t="n">
+      <c r="P10" s="8" t="n">
         <v>1.1116</v>
       </c>
-      <c r="P10" s="12" t="inlineStr">
+      <c r="Q10" s="11" t="inlineStr">
         <is>
           <t>محقق</t>
         </is>
@@ -1253,7 +1278,7 @@
           <t>نسبة %</t>
         </is>
       </c>
-      <c r="F11" s="7" t="n">
+      <c r="F11" s="8" t="n">
         <v>0.4406</v>
       </c>
       <c r="G11" s="9" t="n">
@@ -1268,24 +1293,27 @@
       <c r="J11" s="8" t="n">
         <v>0.4839</v>
       </c>
-      <c r="K11" s="8" t="n">
-        <v>0.5506</v>
+      <c r="K11" s="7" t="n">
+        <v>0.4370000000000001</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>0.8789</v>
-      </c>
-      <c r="M11" s="11" t="inlineStr">
+        <v>0.629</v>
+      </c>
+      <c r="M11" s="8" t="n">
+        <v>0.6948000000000001</v>
+      </c>
+      <c r="N11" s="10" t="inlineStr">
         <is>
           <t>غير محقق</t>
         </is>
       </c>
-      <c r="N11" s="8" t="n">
-        <v>0.5212</v>
-      </c>
       <c r="O11" s="8" t="n">
-        <v>0.9284</v>
-      </c>
-      <c r="P11" s="11" t="inlineStr">
+        <v>0.5479000000000001</v>
+      </c>
+      <c r="P11" s="8" t="n">
+        <v>0.7976000000000001</v>
+      </c>
+      <c r="Q11" s="10" t="inlineStr">
         <is>
           <t>غير محقق</t>
         </is>
@@ -1315,7 +1343,7 @@
           <t>نسبة %</t>
         </is>
       </c>
-      <c r="F12" s="7" t="n">
+      <c r="F12" s="8" t="n">
         <v>0.1591</v>
       </c>
       <c r="G12" s="9" t="n">
@@ -1330,24 +1358,27 @@
       <c r="J12" s="8" t="n">
         <v>0.1735</v>
       </c>
-      <c r="K12" s="8" t="n">
-        <v>0.1591</v>
+      <c r="K12" s="7" t="n">
+        <v>0.142</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>1.0905</v>
-      </c>
-      <c r="M12" s="12" t="inlineStr">
-        <is>
-          <t>محقق</t>
-        </is>
-      </c>
-      <c r="N12" s="8" t="n">
-        <v>0.09449999999999999</v>
+        <v>0.174</v>
+      </c>
+      <c r="M12" s="8" t="n">
+        <v>0.8161</v>
+      </c>
+      <c r="N12" s="10" t="inlineStr">
+        <is>
+          <t>غير محقق</t>
+        </is>
       </c>
       <c r="O12" s="8" t="n">
-        <v>1.836</v>
-      </c>
-      <c r="P12" s="12" t="inlineStr">
+        <v>0.1061</v>
+      </c>
+      <c r="P12" s="8" t="n">
+        <v>1.3384</v>
+      </c>
+      <c r="Q12" s="11" t="inlineStr">
         <is>
           <t>محقق</t>
         </is>
@@ -1393,25 +1424,28 @@
         <v>622</v>
       </c>
       <c r="K13" s="14" t="n">
-        <v>677.7</v>
-      </c>
-      <c r="L13" s="8" t="n">
-        <v>0.9178000000000001</v>
-      </c>
-      <c r="M13" s="11" t="inlineStr">
+        <v>611</v>
+      </c>
+      <c r="L13" s="14" t="n">
+        <v>631</v>
+      </c>
+      <c r="M13" s="8" t="n">
+        <v>0.9682999999999999</v>
+      </c>
+      <c r="N13" s="10" t="inlineStr">
         <is>
           <t>غير محقق</t>
         </is>
       </c>
-      <c r="N13" s="14" t="n">
-        <v>662</v>
-      </c>
-      <c r="O13" s="8" t="n">
-        <v>0.9396</v>
-      </c>
-      <c r="P13" s="11" t="inlineStr">
-        <is>
-          <t>غير محقق</t>
+      <c r="O13" s="14" t="n">
+        <v>609</v>
+      </c>
+      <c r="P13" s="8" t="n">
+        <v>1.0033</v>
+      </c>
+      <c r="Q13" s="11" t="inlineStr">
+        <is>
+          <t>محقق</t>
         </is>
       </c>
     </row>
@@ -1429,9 +1463,9 @@
           <t>قسم الإشراف التربوي</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>مفعل</t>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>غير مفعل</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -1452,24 +1486,25 @@
       <c r="J14" s="8" t="n">
         <v>0.2723</v>
       </c>
-      <c r="K14" s="8" t="n">
+      <c r="K14" s="2" t="n"/>
+      <c r="L14" s="8" t="n">
         <v>0.2686</v>
       </c>
-      <c r="L14" s="8" t="n">
+      <c r="M14" s="8" t="n">
         <v>1.0138</v>
       </c>
-      <c r="M14" s="12" t="inlineStr">
+      <c r="N14" s="11" t="inlineStr">
         <is>
           <t>محقق</t>
         </is>
       </c>
-      <c r="N14" s="8" t="n">
+      <c r="O14" s="8" t="n">
         <v>0.216</v>
       </c>
-      <c r="O14" s="8" t="n">
+      <c r="P14" s="8" t="n">
         <v>1.2606</v>
       </c>
-      <c r="P14" s="12" t="inlineStr">
+      <c r="Q14" s="11" t="inlineStr">
         <is>
           <t>محقق</t>
         </is>
@@ -1489,9 +1524,9 @@
           <t>إدارة تقويم الأداء المعرفي والمهاري</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>مفعل</t>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>غير مفعل</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -1512,24 +1547,25 @@
       <c r="J15" s="9" t="n">
         <v>0.914</v>
       </c>
-      <c r="K15" s="8" t="n">
+      <c r="K15" s="2" t="n"/>
+      <c r="L15" s="8" t="n">
         <v>0.85</v>
       </c>
-      <c r="L15" s="8" t="n">
+      <c r="M15" s="8" t="n">
         <v>1.0753</v>
       </c>
-      <c r="M15" s="12" t="inlineStr">
+      <c r="N15" s="11" t="inlineStr">
         <is>
           <t>محقق</t>
         </is>
       </c>
-      <c r="N15" s="8" t="n">
+      <c r="O15" s="8" t="n">
         <v>0.9</v>
       </c>
-      <c r="O15" s="8" t="n">
+      <c r="P15" s="8" t="n">
         <v>1.0156</v>
       </c>
-      <c r="P15" s="12" t="inlineStr">
+      <c r="Q15" s="11" t="inlineStr">
         <is>
           <t>محقق</t>
         </is>
@@ -1549,9 +1585,9 @@
           <t>إدارة الاستثماروالشراكات</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>مفعل</t>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>غير مفعل</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -1574,24 +1610,25 @@
       <c r="J16" s="7" t="n">
         <v>0.5722</v>
       </c>
-      <c r="K16" s="8" t="n">
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" s="8" t="n">
         <v>0.6526999999999999</v>
       </c>
-      <c r="L16" s="8" t="n">
+      <c r="M16" s="8" t="n">
         <v>0.8767</v>
       </c>
-      <c r="M16" s="11" t="inlineStr">
+      <c r="N16" s="10" t="inlineStr">
         <is>
           <t>غير محقق</t>
         </is>
       </c>
-      <c r="N16" s="8" t="n">
+      <c r="O16" s="8" t="n">
         <v>0.8</v>
       </c>
-      <c r="O16" s="8" t="n">
+      <c r="P16" s="8" t="n">
         <v>0.7153</v>
       </c>
-      <c r="P16" s="11" t="inlineStr">
+      <c r="Q16" s="10" t="inlineStr">
         <is>
           <t>غير محقق</t>
         </is>
@@ -1635,23 +1672,26 @@
         <v>62</v>
       </c>
       <c r="K17" s="14" t="n">
+        <v>62</v>
+      </c>
+      <c r="L17" s="14" t="n">
         <v>69</v>
       </c>
-      <c r="L17" s="8" t="n">
+      <c r="M17" s="8" t="n">
         <v>0.8986</v>
       </c>
-      <c r="M17" s="11" t="inlineStr">
+      <c r="N17" s="10" t="inlineStr">
         <is>
           <t>غير محقق</t>
         </is>
       </c>
-      <c r="N17" s="14" t="n">
+      <c r="O17" s="14" t="n">
         <v>70</v>
       </c>
-      <c r="O17" s="8" t="n">
+      <c r="P17" s="8" t="n">
         <v>0.8856999999999999</v>
       </c>
-      <c r="P17" s="11" t="inlineStr">
+      <c r="Q17" s="10" t="inlineStr">
         <is>
           <t>غير محقق</t>
         </is>
@@ -1671,7 +1711,7 @@
           <t>إدارة الموارد البشرية</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>غير مفعل</t>
         </is>
@@ -1686,32 +1726,33 @@
       <c r="H18" s="2" t="n"/>
       <c r="I18" s="2" t="n"/>
       <c r="J18" s="2" t="n"/>
-      <c r="K18" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L18" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M18" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N18" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O18" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P18" s="10" t="inlineStr">
+      <c r="K18" s="2" t="n"/>
+      <c r="L18" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M18" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N18" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O18" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P18" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q18" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1731,7 +1772,7 @@
           <t>إدارة الموارد البشرية</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D19" s="12" t="inlineStr">
         <is>
           <t>غير مفعل</t>
         </is>
@@ -1746,32 +1787,33 @@
       <c r="H19" s="2" t="n"/>
       <c r="I19" s="2" t="n"/>
       <c r="J19" s="2" t="n"/>
-      <c r="K19" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L19" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M19" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N19" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O19" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P19" s="10" t="inlineStr">
+      <c r="K19" s="2" t="n"/>
+      <c r="L19" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O19" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P19" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q19" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1791,7 +1833,7 @@
           <t>قسم الحضانة</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D20" s="12" t="inlineStr">
         <is>
           <t>غير مفعل</t>
         </is>
@@ -1806,32 +1848,33 @@
       <c r="H20" s="2" t="n"/>
       <c r="I20" s="2" t="n"/>
       <c r="J20" s="2" t="n"/>
-      <c r="K20" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L20" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O20" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P20" s="10" t="inlineStr">
+      <c r="K20" s="2" t="n"/>
+      <c r="L20" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O20" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P20" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q20" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1864,40 +1907,35 @@
       <c r="F21" s="2" t="n"/>
       <c r="G21" s="2" t="n"/>
       <c r="H21" s="2" t="n"/>
-      <c r="I21" s="8" t="n">
+      <c r="I21" s="7" t="n">
         <v>0.9519</v>
       </c>
       <c r="J21" s="8" t="n">
         <v>0.9519</v>
       </c>
-      <c r="K21" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L21" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M21" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="K21" s="9" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="L21" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" s="8" t="n">
+        <v>0.987</v>
       </c>
       <c r="N21" s="10" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O21" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P21" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>غير محقق</t>
+        </is>
+      </c>
+      <c r="O21" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" s="8" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="Q21" s="10" t="inlineStr">
+        <is>
+          <t>غير محقق</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1953,7 @@
           <t>قسم التوجيه الطلابي</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D22" s="12" t="inlineStr">
         <is>
           <t>غير مفعل</t>
         </is>
@@ -1930,32 +1968,33 @@
       <c r="H22" s="2" t="n"/>
       <c r="I22" s="2" t="n"/>
       <c r="J22" s="2" t="n"/>
-      <c r="K22" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L22" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M22" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N22" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O22" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P22" s="10" t="inlineStr">
+      <c r="K22" s="2" t="n"/>
+      <c r="L22" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O22" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P22" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q22" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1975,7 +2014,7 @@
           <t>قسم المسؤولية المجتمعية والعمل التطوعي</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D23" s="12" t="inlineStr">
         <is>
           <t>غير مفعل</t>
         </is>
@@ -1990,32 +2029,33 @@
       <c r="H23" s="2" t="n"/>
       <c r="I23" s="2" t="n"/>
       <c r="J23" s="2" t="n"/>
-      <c r="K23" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L23" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M23" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N23" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O23" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P23" s="10" t="inlineStr">
+      <c r="K23" s="2" t="n"/>
+      <c r="L23" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O23" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P23" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q23" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2035,7 +2075,7 @@
           <t>قسم الإشراف التربوي</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D24" s="12" t="inlineStr">
         <is>
           <t>غير مفعل</t>
         </is>
@@ -2050,32 +2090,33 @@
       <c r="H24" s="2" t="n"/>
       <c r="I24" s="2" t="n"/>
       <c r="J24" s="2" t="n"/>
-      <c r="K24" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L24" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M24" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N24" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O24" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P24" s="10" t="inlineStr">
+      <c r="K24" s="2" t="n"/>
+      <c r="L24" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M24" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N24" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O24" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P24" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q24" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2095,9 +2136,9 @@
           <t>قسم الإدارة المدرسية</t>
         </is>
       </c>
-      <c r="D25" s="16" t="inlineStr">
-        <is>
-          <t>غير مفعل</t>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>مفعل</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
@@ -2116,32 +2157,35 @@
       <c r="J25" s="15" t="n">
         <v>82.18000000000001</v>
       </c>
-      <c r="K25" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L25" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M25" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N25" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O25" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P25" s="10" t="inlineStr">
+      <c r="K25" s="14" t="n">
+        <v>82.18000000000001</v>
+      </c>
+      <c r="L25" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M25" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N25" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O25" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P25" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q25" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2161,7 +2205,7 @@
           <t>مكتب التعليم الخاص</t>
         </is>
       </c>
-      <c r="D26" s="16" t="inlineStr">
+      <c r="D26" s="12" t="inlineStr">
         <is>
           <t>غير مفعل</t>
         </is>
@@ -2176,32 +2220,33 @@
       <c r="H26" s="2" t="n"/>
       <c r="I26" s="2" t="n"/>
       <c r="J26" s="2" t="n"/>
-      <c r="K26" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L26" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M26" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N26" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O26" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P26" s="10" t="inlineStr">
+      <c r="K26" s="2" t="n"/>
+      <c r="L26" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M26" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N26" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O26" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P26" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q26" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2221,7 +2266,7 @@
           <t>إدارة الخدمات المشتركة</t>
         </is>
       </c>
-      <c r="D27" s="16" t="inlineStr">
+      <c r="D27" s="12" t="inlineStr">
         <is>
           <t>غير مفعل</t>
         </is>
@@ -2236,32 +2281,33 @@
       <c r="H27" s="2" t="n"/>
       <c r="I27" s="2" t="n"/>
       <c r="J27" s="2" t="n"/>
-      <c r="K27" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L27" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M27" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N27" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O27" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P27" s="10" t="inlineStr">
+      <c r="K27" s="2" t="n"/>
+      <c r="L27" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M27" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N27" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O27" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P27" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q27" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2281,7 +2327,7 @@
           <t>قسم الإشراف التربوي</t>
         </is>
       </c>
-      <c r="D28" s="16" t="inlineStr">
+      <c r="D28" s="12" t="inlineStr">
         <is>
           <t>غير مفعل</t>
         </is>
@@ -2296,32 +2342,33 @@
       <c r="H28" s="2" t="n"/>
       <c r="I28" s="2" t="n"/>
       <c r="J28" s="2" t="n"/>
-      <c r="K28" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L28" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M28" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N28" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O28" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P28" s="10" t="inlineStr">
+      <c r="K28" s="2" t="n"/>
+      <c r="L28" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M28" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N28" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O28" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P28" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q28" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2341,7 +2388,7 @@
           <t>قسم المخاطر والالتزام</t>
         </is>
       </c>
-      <c r="D29" s="16" t="inlineStr">
+      <c r="D29" s="12" t="inlineStr">
         <is>
           <t>غير مفعل</t>
         </is>
@@ -2356,32 +2403,33 @@
       <c r="H29" s="2" t="n"/>
       <c r="I29" s="2" t="n"/>
       <c r="J29" s="2" t="n"/>
-      <c r="K29" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L29" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M29" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N29" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O29" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P29" s="10" t="inlineStr">
+      <c r="K29" s="2" t="n"/>
+      <c r="L29" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M29" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N29" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O29" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P29" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q29" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2401,7 +2449,7 @@
           <t>قسم المخاطر والالتزام</t>
         </is>
       </c>
-      <c r="D30" s="16" t="inlineStr">
+      <c r="D30" s="12" t="inlineStr">
         <is>
           <t>غير مفعل</t>
         </is>
@@ -2416,32 +2464,33 @@
       <c r="H30" s="2" t="n"/>
       <c r="I30" s="2" t="n"/>
       <c r="J30" s="2" t="n"/>
-      <c r="K30" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L30" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M30" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N30" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O30" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P30" s="10" t="inlineStr">
+      <c r="K30" s="2" t="n"/>
+      <c r="L30" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M30" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N30" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O30" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P30" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q30" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2461,7 +2510,7 @@
           <t>قسم الإشراف التربوي</t>
         </is>
       </c>
-      <c r="D31" s="16" t="inlineStr">
+      <c r="D31" s="12" t="inlineStr">
         <is>
           <t>غير مفعل</t>
         </is>
@@ -2476,32 +2525,33 @@
       <c r="H31" s="2" t="n"/>
       <c r="I31" s="2" t="n"/>
       <c r="J31" s="2" t="n"/>
-      <c r="K31" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L31" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M31" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N31" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O31" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P31" s="10" t="inlineStr">
+      <c r="K31" s="2" t="n"/>
+      <c r="L31" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M31" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N31" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O31" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P31" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q31" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2518,7 +2568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="130" customWidth="1" min="1" max="1"/>
@@ -2527,7 +2577,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="17" t="inlineStr">
         <is>
-          <t>دليل استخدام ملف بيانات المؤشرات — مصدره الرسمي: FxKpi_Data.xlsx</t>
+          <t>دليل استخدام ملف بيانات المؤشرات — آخر تحديث: 20-سبتمبر-2026</t>
         </is>
       </c>
     </row>
@@ -2537,42 +2587,49 @@
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="18" t="inlineStr">
         <is>
-          <t>• جميع بيانات هذا الملف مستخرجة مباشرة من جداول Dim_KPI و Dim_Owners و Fact_KPI_Measurements في الملف الأصلي.</t>
+          <t>• المصدر الرسمي: FxKpi_Data20Sep.xlsx (Dim_KPI, Dim_Owners, Fact_KPI_Measurements, Dim_Period).</t>
         </is>
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="18" t="inlineStr">
         <is>
-          <t>• عمود "القسم" = الجهة المالكة للمؤشر (Dim_Owners عبر owner_ID في Dim_KPI).</t>
+          <t>• تمت إضافة فترة Q1-2026 كآخر فترة فعلية، ومستهدفات FY2026 حيثما توفرت.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
       <c r="A5" s="18" t="inlineStr">
         <is>
-          <t>• "مستهدف جدة" و"مستهدف وطني" = القيمة الخام من Fact_KPI_Measurements (Value_Type = Target_Jeddah / Target_National)، مع تفضيل هدف السنة المالية الأحدث (FY2025) عند توفره.</t>
+          <t>• عدد المؤشرات المفعّلة الآن 13 (بعد تعطيل 6 مؤشرات كانت مفعّلة سابقًا وفق تحديث المصدر).</t>
         </is>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>• "إنجاز المستهدف" = آخر قيمة فعلية متاحة ÷ المستهدف × 100. "الحالة" = محقق إذا بلغ الإنجاز 100% فأكثر، وإلا غير محقق.</t>
+          <t>• قاعدة المستهدف: إن وُجد مستهدف FY2026 لمؤشر/نوع (جدة أو وطني) يُعتمد، وإلا يُستخدم تلقائيًا آخر مستهدف متاح (عادة FY2025) دون أي تدخل يدوي.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>• صفحة الويب المرفقة (kpi_dashboard.html) لا تعتمد على هذا الملف مباشرة، بل على kpi_master_data.csv — إن عدّلت رقمًا هنا في الإكسل، انسخ نفس التعديل إلى ملف CSV ليظهر في الصفحة.</t>
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>• "إنجاز المستهدف" = آخر قيمة فعلية متاحة ÷ المستهدف المعتمد × 100. "الحالة" = محقق إذا بلغ الإنجاز 100% فأكثر، وإلا غير محقق.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
-        <is>
-          <t>• التظليل: أعلى قيمة في كل صف بالتركواز الغامق، وأقل قيمة بالأحمر (تمييز تحذيري فقط).</t>
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>• صفحة الويب المرفقة (kpi_dashboard.html) تعتمد فقط على kpi_master_data.csv؛ أي تعديل هنا في الإكسل يجب نسخه يدويًا إلى CSV، أو إعادة تشغيل سكربت الاستخراج على ملف Excel محدَّث.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="18" t="inlineStr">
+        <is>
+          <t>• التظليل: أعلى قيمة في كل صف بالتركواز الغامق، وأقل قيمة بالأحمر (تمييز تحذيري فقط) — يشمل الآن عمود Q1-2026.</t>
         </is>
       </c>
     </row>
